--- a/data/trans_orig/Q4506_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47590</t>
+          <t>47022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56572</t>
+          <t>56530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61833</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93713</t>
+          <t>94869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>55439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50246</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80112</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85654</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123703</t>
+          <t>124523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45977</t>
+          <t>46271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>85937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119573</t>
+          <t>120351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141597</t>
+          <t>139202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>186278</t>
+          <t>185169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84015</t>
+          <t>84391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59648</t>
+          <t>58822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94616</t>
+          <t>95465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134615</t>
+          <t>133056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229587</t>
+          <t>229860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271476</t>
+          <t>271980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155513</t>
+          <t>153812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196393</t>
+          <t>192613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394325</t>
+          <t>396631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453132</t>
+          <t>453186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>68898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98125</t>
+          <t>98345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140366</t>
+          <t>136498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145063</t>
+          <t>144302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>195361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60575</t>
+          <t>59954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92292</t>
+          <t>94245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>126666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159821</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209485</t>
+          <t>208884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98717</t>
+          <t>97635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139528</t>
+          <t>139741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106534</t>
+          <t>109346</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149630</t>
+          <t>149605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218743</t>
+          <t>216557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>276971</t>
+          <t>276759</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81990</t>
+          <t>82196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>118072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51644</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81858</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141271</t>
+          <t>140812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187917</t>
+          <t>189677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311216</t>
+          <t>310132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366242</t>
+          <t>363620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168810</t>
+          <t>170508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215011</t>
+          <t>216981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>494215</t>
+          <t>495427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567278</t>
+          <t>568067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72022</t>
+          <t>71731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141499</t>
+          <t>139779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183486</t>
+          <t>186910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190835</t>
+          <t>186527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244961</t>
+          <t>244243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>57814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91487</t>
+          <t>94524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124725</t>
+          <t>123733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168605</t>
+          <t>170116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193347</t>
+          <t>192437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247146</t>
+          <t>248624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137945</t>
+          <t>134414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113873</t>
+          <t>112105</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155622</t>
+          <t>155487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>218032</t>
+          <t>218869</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>275690</t>
+          <t>273885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107936</t>
+          <t>107958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63450</t>
+          <t>62164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113333</t>
+          <t>114556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160216</t>
+          <t>158222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322542</t>
+          <t>320545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>373165</t>
+          <t>378170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199176</t>
+          <t>193973</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248648</t>
+          <t>247129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532960</t>
+          <t>531360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606209</t>
+          <t>606084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35441</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66531</t>
+          <t>66162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126470</t>
+          <t>124626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170470</t>
+          <t>167879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167788</t>
+          <t>166229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223787</t>
+          <t>222734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69158</t>
+          <t>70827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55822</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>89435</t>
+          <t>88181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>148539</t>
+          <t>146798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83136</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121216</t>
+          <t>121118</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97515</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138089</t>
+          <t>138256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>190023</t>
+          <t>190249</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>245035</t>
+          <t>247644</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>94758</t>
+          <t>94688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70702</t>
+          <t>71579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107008</t>
+          <t>109439</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154459</t>
+          <t>154291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>308298</t>
+          <t>309803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>359162</t>
+          <t>360842</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202073</t>
+          <t>202902</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254369</t>
+          <t>254412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>525078</t>
+          <t>519012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>601253</t>
+          <t>599817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>27770</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>74692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111712</t>
+          <t>109663</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>109798</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153944</t>
+          <t>156534</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23606</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>49439</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80852</t>
+          <t>78739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76226</t>
+          <t>77625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116975</t>
+          <t>116287</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67977</t>
+          <t>67259</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>67085</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99178</t>
+          <t>99601</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>112317</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>157076</t>
+          <t>155251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43993</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41216</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>71132</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106692</t>
+          <t>108226</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>224613</t>
+          <t>224071</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>267252</t>
+          <t>266596</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>160531</t>
+          <t>160494</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>207046</t>
+          <t>203065</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>398251</t>
+          <t>395886</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>458637</t>
+          <t>458312</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>41292</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>64948</t>
+          <t>61951</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>97316</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>89015</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>129831</t>
+          <t>129105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82233</t>
+          <t>82006</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>57624</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>64613</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>75689</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>112869</t>
+          <t>113757</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27132</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>82376</t>
+          <t>82341</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>170364</t>
+          <t>168714</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>207392</t>
+          <t>206619</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>123522</t>
+          <t>121846</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>160758</t>
+          <t>161725</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>302747</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>358448</t>
+          <t>355538</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>82816</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>61652</t>
+          <t>59656</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94496</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27178</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>39928</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>34077</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>40297</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>57297</t>
+          <t>56704</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>89108</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>34596</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>67112</t>
+          <t>66348</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>153971</t>
+          <t>154718</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>185589</t>
+          <t>184660</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>198849</t>
+          <t>198177</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>237701</t>
+          <t>239162</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>363683</t>
+          <t>364238</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>414111</t>
+          <t>413096</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>237938</t>
+          <t>238341</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>301895</t>
+          <t>299975</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>664050</t>
+          <t>661393</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>763842</t>
+          <t>760420</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>911490</t>
+          <t>916521</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1036080</t>
+          <t>1034154</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>284114</t>
+          <t>284021</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>355489</t>
+          <t>351772</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>473793</t>
+          <t>478189</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>562163</t>
+          <t>562433</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>781497</t>
+          <t>785808</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>896064</t>
+          <t>900498</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>478571</t>
+          <t>470397</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>560521</t>
+          <t>561053</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>606279</t>
+          <t>612613</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>706445</t>
+          <t>704010</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1109561</t>
+          <t>1108717</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1232492</t>
+          <t>1243764</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>399099</t>
+          <t>402097</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>479721</t>
+          <t>481800</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>274124</t>
+          <t>272407</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>345549</t>
+          <t>343370</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>697688</t>
+          <t>695039</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>797203</t>
+          <t>805493</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1814187</t>
+          <t>1822258</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1936800</t>
+          <t>1937460</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1301182</t>
+          <t>1297622</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1419311</t>
+          <t>1415904</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3151595</t>
+          <t>3159503</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3320533</t>
+          <t>3326108</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50357</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>58849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89758</t>
+          <t>89005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>92322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132840</t>
+          <t>129378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72330</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104992</t>
+          <t>108621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>103796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140279</t>
+          <t>139014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185996</t>
+          <t>186494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235154</t>
+          <t>234229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63528</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>94822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62464</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>135829</t>
+          <t>135653</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177869</t>
+          <t>179128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>42356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70435</t>
+          <t>70953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26510</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>76214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111879</t>
+          <t>114394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139781</t>
+          <t>136434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177817</t>
+          <t>176731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71856</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106323</t>
+          <t>100864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>218523</t>
+          <t>218337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267741</t>
+          <t>270379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>45824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73884</t>
+          <t>74621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94327</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131920</t>
+          <t>131799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147884</t>
+          <t>147645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194157</t>
+          <t>194342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120917</t>
+          <t>119480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163756</t>
+          <t>161656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158749</t>
+          <t>159966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200249</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290562</t>
+          <t>288326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350314</t>
+          <t>347177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90651</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131841</t>
+          <t>131648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94847</t>
+          <t>95083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129122</t>
+          <t>130570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193942</t>
+          <t>197260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>250352</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61268</t>
+          <t>62349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94317</t>
+          <t>95510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57256</t>
+          <t>54770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100844</t>
+          <t>100841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143976</t>
+          <t>143391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177668</t>
+          <t>177493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226213</t>
+          <t>224675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>98877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135834</t>
+          <t>137015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288075</t>
+          <t>285910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348984</t>
+          <t>344708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>84733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125551</t>
+          <t>125169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150061</t>
+          <t>148615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192337</t>
+          <t>193495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245531</t>
+          <t>244855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301743</t>
+          <t>301941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132242</t>
+          <t>131047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175475</t>
+          <t>174596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165035</t>
+          <t>163903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211454</t>
+          <t>210707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308328</t>
+          <t>309292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373348</t>
+          <t>371238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95095</t>
+          <t>94962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133560</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106579</t>
+          <t>105256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146036</t>
+          <t>145592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>211336</t>
+          <t>209834</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>267169</t>
+          <t>265143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71836</t>
+          <t>71656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106328</t>
+          <t>110097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36271</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63096</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115746</t>
+          <t>117956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>161248</t>
+          <t>164142</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182630</t>
+          <t>181679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230681</t>
+          <t>231016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109345</t>
+          <t>109145</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151269</t>
+          <t>149614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302184</t>
+          <t>305041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368434</t>
+          <t>367144</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82393</t>
+          <t>83567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126498</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171009</t>
+          <t>169355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>185755</t>
+          <t>186809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240448</t>
+          <t>241628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100309</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141094</t>
+          <t>141508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154818</t>
+          <t>150717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198985</t>
+          <t>196722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264590</t>
+          <t>262406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>327333</t>
+          <t>325017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90099</t>
+          <t>89072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129705</t>
+          <t>128055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>102038</t>
+          <t>102565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142725</t>
+          <t>142336</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>199621</t>
+          <t>203410</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256090</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85201</t>
+          <t>85324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>49513</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80588</t>
+          <t>79532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>109524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>155494</t>
+          <t>154378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254282</t>
+          <t>258795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>309643</t>
+          <t>310003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121149</t>
+          <t>121922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165022</t>
+          <t>165251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>391046</t>
+          <t>392017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>459231</t>
+          <t>462533</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93690</t>
+          <t>95344</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>134052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123298</t>
+          <t>122347</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>171401</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90940</t>
+          <t>91198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>104265</t>
+          <t>106660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145757</t>
+          <t>147266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>172362</t>
+          <t>174315</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>225294</t>
+          <t>227180</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>55069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66813</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101173</t>
+          <t>99598</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>132194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>179656</t>
+          <t>179521</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>45824</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46957</t>
+          <t>46044</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>74680</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>112506</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>216560</t>
+          <t>218518</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>260692</t>
+          <t>263892</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>118637</t>
+          <t>118278</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>161275</t>
+          <t>160403</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>345946</t>
+          <t>347049</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>410971</t>
+          <t>412070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>89398</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>83169</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121660</t>
+          <t>119174</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>66635</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>98966</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>105246</t>
+          <t>105249</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>148434</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70643</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>70361</t>
+          <t>70887</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>107944</t>
+          <t>106748</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>49177</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>78264</t>
+          <t>79217</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>178056</t>
+          <t>176838</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>214286</t>
+          <t>211340</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>119659</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>157182</t>
+          <t>155805</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>304843</t>
+          <t>307701</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>362211</t>
+          <t>360568</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>63943</t>
+          <t>64615</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>43347</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>67572</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>104466</t>
+          <t>101655</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>37832</t>
+          <t>37656</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>70273</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>90655</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10868,12 +10868,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>162795</t>
+          <t>163322</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>190933</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>187860</t>
+          <t>189297</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>234174</t>
+          <t>235998</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>362514</t>
+          <t>362856</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>416136</t>
+          <t>415003</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>297102</t>
+          <t>301654</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>370333</t>
+          <t>371322</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>682798</t>
+          <t>689529</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>791879</t>
+          <t>784511</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1006133</t>
+          <t>1005046</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1133260</t>
+          <t>1134760</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>601741</t>
+          <t>602023</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>695710</t>
+          <t>692471</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>869804</t>
+          <t>868070</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>974100</t>
+          <t>977602</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1493335</t>
+          <t>1500954</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1637378</t>
+          <t>1639322</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>491122</t>
+          <t>492040</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>579815</t>
+          <t>579463</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>577867</t>
+          <t>578316</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>668512</t>
+          <t>668315</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1099234</t>
+          <t>1101547</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1221363</t>
+          <t>1222539</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>360855</t>
+          <t>364918</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>436974</t>
+          <t>441971</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>252221</t>
+          <t>254995</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>317800</t>
+          <t>323173</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>635888</t>
+          <t>637369</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>739363</t>
+          <t>737097</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1397019</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1519989</t>
+          <t>1511904</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>908037</t>
+          <t>908927</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1016855</t>
+          <t>1016924</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2343967</t>
+          <t>2344262</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2506472</t>
+          <t>2502378</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4506_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32757</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56530</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94869</t>
+          <t>94823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>86498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124523</t>
+          <t>125716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74670</t>
+          <t>76802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85937</t>
+          <t>86412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120351</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139202</t>
+          <t>139960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>185169</t>
+          <t>185281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84391</t>
+          <t>85019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95465</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133056</t>
+          <t>135169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229860</t>
+          <t>229916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271980</t>
+          <t>272468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153812</t>
+          <t>154253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192613</t>
+          <t>193973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396631</t>
+          <t>397507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453186</t>
+          <t>455283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68898</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98345</t>
+          <t>97558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136498</t>
+          <t>138636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144302</t>
+          <t>144851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195361</t>
+          <t>194786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>60635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94245</t>
+          <t>93595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87403</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126666</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158893</t>
+          <t>156571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208884</t>
+          <t>209239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97635</t>
+          <t>98273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139741</t>
+          <t>140110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109346</t>
+          <t>109132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>150749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216557</t>
+          <t>219059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>276759</t>
+          <t>275478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82196</t>
+          <t>81125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118072</t>
+          <t>118551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>51325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>143526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189677</t>
+          <t>190678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310132</t>
+          <t>308967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363620</t>
+          <t>364637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170508</t>
+          <t>168774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216981</t>
+          <t>216318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>495427</t>
+          <t>493184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>568067</t>
+          <t>566400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>41921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139779</t>
+          <t>139820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186910</t>
+          <t>185942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186527</t>
+          <t>189148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244243</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57814</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94524</t>
+          <t>91324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123733</t>
+          <t>122965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170116</t>
+          <t>166620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192437</t>
+          <t>191980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>250064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134414</t>
+          <t>136391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112105</t>
+          <t>112780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155487</t>
+          <t>156313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>218869</t>
+          <t>218169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273885</t>
+          <t>276599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>106146</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>34337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62164</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>113495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158222</t>
+          <t>157654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320545</t>
+          <t>317507</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>378170</t>
+          <t>373682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193973</t>
+          <t>198507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247129</t>
+          <t>249595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531360</t>
+          <t>534596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606084</t>
+          <t>609269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>63640</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124626</t>
+          <t>125929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167879</t>
+          <t>169948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166229</t>
+          <t>170669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222734</t>
+          <t>223425</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>40510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>72106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88181</t>
+          <t>88219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102186</t>
+          <t>101766</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146798</t>
+          <t>146958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121118</t>
+          <t>121892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97939</t>
+          <t>97263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138256</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>190249</t>
+          <t>193072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>247644</t>
+          <t>248446</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60032</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>70563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>109439</t>
+          <t>109814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154291</t>
+          <t>155086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>309803</t>
+          <t>308136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>360842</t>
+          <t>359142</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202902</t>
+          <t>201224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254412</t>
+          <t>253839</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>519012</t>
+          <t>525876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>599817</t>
+          <t>597060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51831</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74692</t>
+          <t>76552</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109663</t>
+          <t>111036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>111159</t>
+          <t>109613</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>156534</t>
+          <t>154108</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>48674</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>47490</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78739</t>
+          <t>78262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77625</t>
+          <t>77975</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116287</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67259</t>
+          <t>69991</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99601</t>
+          <t>99735</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>112317</t>
+          <t>112803</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155251</t>
+          <t>156585</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>45263</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>70758</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>108226</t>
+          <t>107359</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>224071</t>
+          <t>225435</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>266596</t>
+          <t>266934</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>160494</t>
+          <t>159304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>203065</t>
+          <t>203528</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>395886</t>
+          <t>399632</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>458312</t>
+          <t>459532</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>41292</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>95117</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>90785</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>129105</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57028</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>53705</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82006</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57624</t>
+          <t>58451</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>37866</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>64163</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>113757</t>
+          <t>111608</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>51363</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>51373</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>82341</t>
+          <t>82224</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>168714</t>
+          <t>170930</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>206619</t>
+          <t>207517</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>123832</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>161725</t>
+          <t>160026</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>302747</t>
+          <t>304778</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>355538</t>
+          <t>357251</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>52331</t>
+          <t>51988</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>82748</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>59656</t>
+          <t>63337</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>94496</t>
+          <t>96032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>39928</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>60481</t>
+          <t>60388</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40297</t>
+          <t>40722</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>56704</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>89108</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>34596</t>
+          <t>35457</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>38159</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>66348</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>154718</t>
+          <t>153401</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>184660</t>
+          <t>184375</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>198177</t>
+          <t>199487</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>239162</t>
+          <t>240551</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>364238</t>
+          <t>362910</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>413096</t>
+          <t>411490</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>238341</t>
+          <t>237615</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>299975</t>
+          <t>301341</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>661393</t>
+          <t>660646</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>760420</t>
+          <t>762143</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>916521</t>
+          <t>916001</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1034154</t>
+          <t>1042034</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>284021</t>
+          <t>284772</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>351772</t>
+          <t>354953</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>478189</t>
+          <t>477316</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>562433</t>
+          <t>565190</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>785808</t>
+          <t>772834</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>900498</t>
+          <t>893190</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>470397</t>
+          <t>474972</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>561053</t>
+          <t>560350</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>612613</t>
+          <t>610985</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>704010</t>
+          <t>706379</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1108717</t>
+          <t>1108671</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1243764</t>
+          <t>1242232</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>402097</t>
+          <t>399369</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>481800</t>
+          <t>481606</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>272407</t>
+          <t>271802</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>343370</t>
+          <t>340699</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>695039</t>
+          <t>697794</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>805493</t>
+          <t>803616</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1822258</t>
+          <t>1814879</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1937460</t>
+          <t>1941264</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1297622</t>
+          <t>1301373</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1415904</t>
+          <t>1419168</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3159503</t>
+          <t>3154236</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3326108</t>
+          <t>3330002</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89005</t>
+          <t>89563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92322</t>
+          <t>93569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129378</t>
+          <t>130530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73615</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108621</t>
+          <t>108131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103796</t>
+          <t>104112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139014</t>
+          <t>141235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186494</t>
+          <t>185719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234229</t>
+          <t>235552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>63684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94822</t>
+          <t>95099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64298</t>
+          <t>62352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>92536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>135653</t>
+          <t>134478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179128</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42356</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>71102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50538</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>75088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114394</t>
+          <t>111739</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136434</t>
+          <t>136205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176731</t>
+          <t>176880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70743</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100864</t>
+          <t>101361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>218337</t>
+          <t>218673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270379</t>
+          <t>270983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>73695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94481</t>
+          <t>93035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131799</t>
+          <t>130745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147645</t>
+          <t>147070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194342</t>
+          <t>194070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119480</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161656</t>
+          <t>160867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159966</t>
+          <t>157855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>199880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288326</t>
+          <t>289604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>347177</t>
+          <t>349071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91981</t>
+          <t>92277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131648</t>
+          <t>130948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130570</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>197260</t>
+          <t>195122</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250352</t>
+          <t>248246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>64339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95510</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>56156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100841</t>
+          <t>100026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143391</t>
+          <t>143069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177493</t>
+          <t>178848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224675</t>
+          <t>223644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98877</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137015</t>
+          <t>135883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285910</t>
+          <t>287941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344708</t>
+          <t>347431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84733</t>
+          <t>87216</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>124241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148615</t>
+          <t>148831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>191882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244855</t>
+          <t>246413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301941</t>
+          <t>306543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131047</t>
+          <t>131684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174596</t>
+          <t>176590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163903</t>
+          <t>165751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210707</t>
+          <t>211704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309292</t>
+          <t>306571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>371238</t>
+          <t>370609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94962</t>
+          <t>94961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136043</t>
+          <t>133315</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105256</t>
+          <t>106284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145592</t>
+          <t>145936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>209834</t>
+          <t>213059</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>265143</t>
+          <t>268812</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71656</t>
+          <t>73090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110097</t>
+          <t>108893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62183</t>
+          <t>62071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117956</t>
+          <t>114602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164142</t>
+          <t>159421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181679</t>
+          <t>183332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231016</t>
+          <t>231046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>110626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149614</t>
+          <t>151944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305041</t>
+          <t>306364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367144</t>
+          <t>368299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50121</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83567</t>
+          <t>84038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125518</t>
+          <t>126759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169355</t>
+          <t>170532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186809</t>
+          <t>186485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241628</t>
+          <t>240729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>101973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150717</t>
+          <t>152018</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196722</t>
+          <t>197811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262406</t>
+          <t>261863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>325017</t>
+          <t>324974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89072</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128055</t>
+          <t>127833</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>102565</t>
+          <t>100570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142336</t>
+          <t>142227</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>203410</t>
+          <t>202176</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259495</t>
+          <t>258176</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53033</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85324</t>
+          <t>84529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>48622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79532</t>
+          <t>79836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>109524</t>
+          <t>112157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154378</t>
+          <t>157448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>258795</t>
+          <t>257438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>310003</t>
+          <t>312075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121922</t>
+          <t>123117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165251</t>
+          <t>164587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>392017</t>
+          <t>390917</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>462533</t>
+          <t>461753</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>46380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95344</t>
+          <t>95692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134052</t>
+          <t>136994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>122347</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>171401</t>
+          <t>172970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91198</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106660</t>
+          <t>101811</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147266</t>
+          <t>145267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>174315</t>
+          <t>173652</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227180</t>
+          <t>225738</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55069</t>
+          <t>56415</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>90465</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65610</t>
+          <t>65733</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99598</t>
+          <t>100826</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>131398</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>179521</t>
+          <t>181260</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>74110</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46044</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>74680</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>112506</t>
+          <t>113078</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>218518</t>
+          <t>216079</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>263892</t>
+          <t>260586</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>118278</t>
+          <t>118960</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>160403</t>
+          <t>163298</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>347049</t>
+          <t>347273</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>412070</t>
+          <t>410521</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>57208</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>89398</t>
+          <t>88854</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>82381</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>120586</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>66635</t>
+          <t>65914</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>100136</t>
+          <t>100644</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>105249</t>
+          <t>105718</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>148434</t>
+          <t>148270</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70072</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>106748</t>
+          <t>109564</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>49177</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>80588</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>176838</t>
+          <t>175758</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>211340</t>
+          <t>212800</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>119659</t>
+          <t>119579</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>155805</t>
+          <t>156118</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>307701</t>
+          <t>306020</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>360568</t>
+          <t>360868</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>67330</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43347</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76257</t>
+          <t>76898</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>40228</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>70205</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>65909</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>101655</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>70273</t>
+          <t>69240</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>58103</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>91410</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10868,12 +10868,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>44518</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>33932</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>61669</t>
+          <t>65289</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>163322</t>
+          <t>161807</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>190933</t>
+          <t>188820</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>189297</t>
+          <t>187423</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>235998</t>
+          <t>235969</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>362856</t>
+          <t>362488</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>415003</t>
+          <t>416648</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>301654</t>
+          <t>302487</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>371322</t>
+          <t>372784</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>689529</t>
+          <t>692019</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>784511</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1005046</t>
+          <t>1008203</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1134760</t>
+          <t>1134726</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>602023</t>
+          <t>603562</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>692471</t>
+          <t>694636</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>868070</t>
+          <t>867576</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>977602</t>
+          <t>976943</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1500954</t>
+          <t>1496288</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1639322</t>
+          <t>1647704</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>492040</t>
+          <t>487993</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>576780</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>578316</t>
+          <t>580591</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>668315</t>
+          <t>670217</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1101547</t>
+          <t>1095896</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1222539</t>
+          <t>1223810</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>364918</t>
+          <t>361922</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>441971</t>
+          <t>438995</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>254995</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>323173</t>
+          <t>321140</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>637369</t>
+          <t>640149</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>737097</t>
+          <t>739219</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1399609</t>
+          <t>1404912</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1511904</t>
+          <t>1517238</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>908927</t>
+          <t>909067</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1016924</t>
+          <t>1019554</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2344262</t>
+          <t>2338813</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2502378</t>
+          <t>2499960</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
